--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123927965</v>
+        <v>123927598</v>
       </c>
       <c r="B2" t="n">
-        <v>100682</v>
+        <v>109772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>222776</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,14 +715,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrevikskilen vid landsvägen, Boh</t>
+          <t>Orreviksskilen sydväst om sommarstugan, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>282172</v>
+        <v>282343</v>
       </c>
       <c r="R2" t="n">
-        <v>6529251</v>
+        <v>6529290</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
         <v>123925720</v>
       </c>
       <c r="B3" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123927598</v>
+        <v>123927965</v>
       </c>
       <c r="B4" t="n">
-        <v>110197</v>
+        <v>100257</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222776</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,14 +929,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orreviksskilen sydväst om sommarstugan, Boh</t>
+          <t>Orrevikskilen vid landsvägen, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>282343</v>
+        <v>282172</v>
       </c>
       <c r="R4" t="n">
-        <v>6529290</v>
+        <v>6529251</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123927598</v>
+        <v>123927965</v>
       </c>
       <c r="B2" t="n">
-        <v>109772</v>
+        <v>100257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222776</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,14 +715,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orreviksskilen sydväst om sommarstugan, Boh</t>
+          <t>Orrevikskilen vid landsvägen, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>282343</v>
+        <v>282172</v>
       </c>
       <c r="R2" t="n">
-        <v>6529290</v>
+        <v>6529251</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123927965</v>
+        <v>123927598</v>
       </c>
       <c r="B4" t="n">
-        <v>100257</v>
+        <v>109775</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>222776</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,14 +929,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrevikskilen vid landsvägen, Boh</t>
+          <t>Orreviksskilen sydväst om sommarstugan, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>282172</v>
+        <v>282343</v>
       </c>
       <c r="R4" t="n">
-        <v>6529251</v>
+        <v>6529290</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123927965</v>
+        <v>123927762</v>
       </c>
       <c r="B2" t="n">
         <v>100257</v>
@@ -892,7 +892,7 @@
         <v>123927598</v>
       </c>
       <c r="B4" t="n">
-        <v>109775</v>
+        <v>109776</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123927965</v>
+        <v>123927598</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
+        <v>109798</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>222776</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,14 +715,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrevikskilen vid landsvägen, Boh</t>
+          <t>Orreviksskilen sydväst om sommarstugan, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>282172</v>
+        <v>282343</v>
       </c>
       <c r="R2" t="n">
-        <v>6529251</v>
+        <v>6529290</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123927598</v>
+        <v>123927762</v>
       </c>
       <c r="B4" t="n">
-        <v>109798</v>
+        <v>100279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222776</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,14 +929,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orreviksskilen sydväst om sommarstugan, Boh</t>
+          <t>Orrevikskilen vid landsvägen, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>282343</v>
+        <v>282172</v>
       </c>
       <c r="R4" t="n">
-        <v>6529290</v>
+        <v>6529251</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123927598</v>
+        <v>123925720</v>
       </c>
       <c r="B2" t="n">
-        <v>109798</v>
+        <v>100279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222776</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,14 +715,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orreviksskilen sydväst om sommarstugan, Boh</t>
+          <t>Orrevikskilen norr om sommarstugan, Orrevikskil, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>282343</v>
+        <v>282434</v>
       </c>
       <c r="R2" t="n">
-        <v>6529290</v>
+        <v>6529442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123925720</v>
+        <v>123927965</v>
       </c>
       <c r="B3" t="n">
         <v>100279</v>
@@ -822,14 +822,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrevikskilen norr om sommarstugan, Orrevikskil, Boh</t>
+          <t>Orrevikskilen vid landsvägen, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>282434</v>
+        <v>282172</v>
       </c>
       <c r="R3" t="n">
-        <v>6529442</v>
+        <v>6529251</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123927762</v>
+        <v>123927598</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>109798</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>222776</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,14 +929,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrevikskilen vid landsvägen, Boh</t>
+          <t>Orreviksskilen sydväst om sommarstugan, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>282172</v>
+        <v>282343</v>
       </c>
       <c r="R4" t="n">
-        <v>6529251</v>
+        <v>6529290</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123925720</v>
+        <v>123927762</v>
       </c>
       <c r="B2" t="n">
         <v>100279</v>
@@ -715,14 +715,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrevikskilen norr om sommarstugan, Orrevikskil, Boh</t>
+          <t>Orrevikskilen vid landsvägen, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>282434</v>
+        <v>282172</v>
       </c>
       <c r="R2" t="n">
-        <v>6529442</v>
+        <v>6529251</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123927965</v>
+        <v>123927598</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
+        <v>109798</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>222776</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,14 +822,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrevikskilen vid landsvägen, Boh</t>
+          <t>Orreviksskilen sydväst om sommarstugan, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>282172</v>
+        <v>282343</v>
       </c>
       <c r="R3" t="n">
-        <v>6529251</v>
+        <v>6529290</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123927598</v>
+        <v>123925720</v>
       </c>
       <c r="B4" t="n">
-        <v>109798</v>
+        <v>100279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222776</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,14 +929,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orreviksskilen sydväst om sommarstugan, Boh</t>
+          <t>Orrevikskilen norr om sommarstugan, Orrevikskil, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>282343</v>
+        <v>282434</v>
       </c>
       <c r="R4" t="n">
-        <v>6529290</v>
+        <v>6529442</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123927598</v>
+        <v>123925720</v>
       </c>
       <c r="B3" t="n">
-        <v>109798</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222776</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,14 +822,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orreviksskilen sydväst om sommarstugan, Boh</t>
+          <t>Orrevikskilen norr om sommarstugan, Orrevikskil, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>282343</v>
+        <v>282434</v>
       </c>
       <c r="R3" t="n">
-        <v>6529290</v>
+        <v>6529442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123925720</v>
+        <v>123927598</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>109798</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>222776</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,14 +929,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrevikskilen norr om sommarstugan, Orrevikskil, Boh</t>
+          <t>Orreviksskilen sydväst om sommarstugan, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>282434</v>
+        <v>282343</v>
       </c>
       <c r="R4" t="n">
-        <v>6529442</v>
+        <v>6529290</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -994,6 +994,455 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126369740</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56811</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102932</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kricka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Anas crecca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Orrevikskil, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>282451</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6529490</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tjärnö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Martin Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Martin Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126369716</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57602</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Orrevikskil, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>282451</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6529490</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tjärnö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Martin Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Martin Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126369748</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57000</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102950</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Strandskata</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Haematopus ostralegus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Orrevikskil, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>282451</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6529490</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tjärnö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Martin Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Martin Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126369770</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56719</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102930</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gravand</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Orrevikskil, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>282451</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6529490</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tjärnö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Martin Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Martin Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>126369740</v>
       </c>
       <c r="B5" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>126369716</v>
       </c>
       <c r="B6" t="n">
-        <v>57602</v>
+        <v>57603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>126369748</v>
       </c>
       <c r="B7" t="n">
-        <v>57000</v>
+        <v>57001</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>126369770</v>
       </c>
       <c r="B8" t="n">
-        <v>56719</v>
+        <v>56720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -1110,7 +1110,7 @@
         <v>126369716</v>
       </c>
       <c r="B6" t="n">
-        <v>57603</v>
+        <v>57607</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -1110,7 +1110,7 @@
         <v>126369716</v>
       </c>
       <c r="B6" t="n">
-        <v>57607</v>
+        <v>57609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -1110,7 +1110,7 @@
         <v>126369716</v>
       </c>
       <c r="B6" t="n">
-        <v>57609</v>
+        <v>57612</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -1110,7 +1110,7 @@
         <v>126369716</v>
       </c>
       <c r="B6" t="n">
-        <v>57612</v>
+        <v>57618</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -1110,7 +1110,7 @@
         <v>126369716</v>
       </c>
       <c r="B6" t="n">
-        <v>57618</v>
+        <v>57603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -1445,50 +1445,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133021649</v>
+        <v>133025036</v>
       </c>
       <c r="B9" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Orrevikskilens naturreservat, Orrevikskilens naturreservat, Boh</t>
+          <t>Orrevikskil, Orrevikskil, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>282143</v>
+        <v>282329</v>
       </c>
       <c r="R9" t="n">
-        <v>6529207</v>
+        <v>6529317</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1534,17 +1533,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Dead tree stem</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1562,49 +1551,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133025036</v>
+        <v>133021649</v>
       </c>
       <c r="B10" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Orrevikskil, Orrevikskil, Boh</t>
+          <t>Orrevikskilens naturreservat, Orrevikskilens naturreservat, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>282329</v>
+        <v>282143</v>
       </c>
       <c r="R10" t="n">
-        <v>6529317</v>
+        <v>6529207</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1650,7 +1640,17 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Dead tree stem</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -1445,49 +1445,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133025036</v>
+        <v>133021649</v>
       </c>
       <c r="B9" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Orrevikskil, Orrevikskil, Boh</t>
+          <t>Orrevikskilens naturreservat, Orrevikskilens naturreservat, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>282329</v>
+        <v>282143</v>
       </c>
       <c r="R9" t="n">
-        <v>6529317</v>
+        <v>6529207</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1533,7 +1534,17 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Dead tree stem</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1551,50 +1562,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133021649</v>
+        <v>133025036</v>
       </c>
       <c r="B10" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Orrevikskilens naturreservat, Orrevikskilens naturreservat, Boh</t>
+          <t>Orrevikskil, Orrevikskil, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>282143</v>
+        <v>282329</v>
       </c>
       <c r="R10" t="n">
-        <v>6529207</v>
+        <v>6529317</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1640,17 +1650,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Dead tree stem</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -1565,7 +1565,7 @@
         <v>133025036</v>
       </c>
       <c r="B10" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>133022532</v>
       </c>
       <c r="B11" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -1445,50 +1445,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133021649</v>
+        <v>133025036</v>
       </c>
       <c r="B9" t="n">
-        <v>57955</v>
+        <v>99140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Orrevikskilens naturreservat, Orrevikskilens naturreservat, Boh</t>
+          <t>Orrevikskil, Orrevikskil, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>282143</v>
+        <v>282329</v>
       </c>
       <c r="R9" t="n">
-        <v>6529207</v>
+        <v>6529317</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1534,17 +1533,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Dead tree stem</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1562,49 +1551,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133025036</v>
+        <v>133021649</v>
       </c>
       <c r="B10" t="n">
-        <v>99132</v>
+        <v>57955</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Orrevikskil, Orrevikskil, Boh</t>
+          <t>Orrevikskilens naturreservat, Orrevikskilens naturreservat, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>282329</v>
+        <v>282143</v>
       </c>
       <c r="R10" t="n">
-        <v>6529317</v>
+        <v>6529207</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1650,7 +1640,17 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Dead tree stem</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1671,7 +1671,7 @@
         <v>133022532</v>
       </c>
       <c r="B11" t="n">
-        <v>101340</v>
+        <v>101348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -1445,49 +1445,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133025036</v>
+        <v>133021649</v>
       </c>
       <c r="B9" t="n">
-        <v>99140</v>
+        <v>57955</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Orrevikskil, Orrevikskil, Boh</t>
+          <t>Orrevikskilens naturreservat, Orrevikskilens naturreservat, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>282329</v>
+        <v>282143</v>
       </c>
       <c r="R9" t="n">
-        <v>6529317</v>
+        <v>6529207</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1533,7 +1534,17 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Dead tree stem</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1551,50 +1562,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133021649</v>
+        <v>133025036</v>
       </c>
       <c r="B10" t="n">
-        <v>57955</v>
+        <v>99140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Orrevikskilens naturreservat, Orrevikskilens naturreservat, Boh</t>
+          <t>Orrevikskil, Orrevikskil, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>282143</v>
+        <v>282329</v>
       </c>
       <c r="R10" t="n">
-        <v>6529207</v>
+        <v>6529317</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1640,17 +1650,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Dead tree stem</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 10368-2025 artfynd.xlsx
+++ b/artfynd/A 10368-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133021649</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133024830</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126369716</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126369770</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126369740</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1345,6 +1375,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126369748</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133025036</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1553,6 +1593,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123925720</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1655,6 +1700,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123927762</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1771,6 +1821,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133022532</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1873,6 +1928,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123926079</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1975,8 +2035,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123927598</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>